--- a/artfynd/A 18628-2024 artfynd.xlsx
+++ b/artfynd/A 18628-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980610</v>
+        <v>117980690</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593545</v>
+        <v>593650</v>
       </c>
       <c r="R3" t="n">
-        <v>6982237</v>
+        <v>6982111</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -887,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117980690</v>
+        <v>117980610</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,34 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Gussjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593650</v>
+        <v>593545</v>
       </c>
       <c r="R4" t="n">
-        <v>6982111</v>
+        <v>6982237</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>

--- a/artfynd/A 18628-2024 artfynd.xlsx
+++ b/artfynd/A 18628-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117980689</v>
+        <v>117980690</v>
       </c>
       <c r="B2" t="n">
         <v>78480</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593417</v>
+        <v>593650</v>
       </c>
       <c r="R2" t="n">
-        <v>6982462</v>
+        <v>6982111</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980690</v>
+        <v>117980710</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593650</v>
+        <v>593517</v>
       </c>
       <c r="R3" t="n">
-        <v>6982111</v>
+        <v>6982298</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117980676</v>
+        <v>117980587</v>
       </c>
       <c r="B5" t="n">
-        <v>56270</v>
+        <v>90464</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208260</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593679</v>
+        <v>593543</v>
       </c>
       <c r="R5" t="n">
-        <v>6982094</v>
+        <v>6982242</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980587</v>
+        <v>117980680</v>
       </c>
       <c r="B6" t="n">
-        <v>90464</v>
+        <v>90648</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593543</v>
+        <v>593615</v>
       </c>
       <c r="R6" t="n">
-        <v>6982242</v>
+        <v>6982085</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980680</v>
+        <v>117980689</v>
       </c>
       <c r="B7" t="n">
-        <v>90648</v>
+        <v>78480</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593615</v>
+        <v>593417</v>
       </c>
       <c r="R7" t="n">
-        <v>6982085</v>
+        <v>6982462</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117980637</v>
+        <v>117980676</v>
       </c>
       <c r="B8" t="n">
-        <v>78217</v>
+        <v>56270</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>208260</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593440</v>
+        <v>593679</v>
       </c>
       <c r="R8" t="n">
-        <v>6982406</v>
+        <v>6982094</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117980710</v>
+        <v>117980637</v>
       </c>
       <c r="B9" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1409,25 +1409,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593517</v>
+        <v>593440</v>
       </c>
       <c r="R9" t="n">
-        <v>6982298</v>
+        <v>6982406</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>

--- a/artfynd/A 18628-2024 artfynd.xlsx
+++ b/artfynd/A 18628-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117980690</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117980710</v>
+        <v>117980676</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>56270</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>208260</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593517</v>
+        <v>593679</v>
       </c>
       <c r="R3" t="n">
-        <v>6982298</v>
+        <v>6982094</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -882,7 +882,7 @@
         <v>117980610</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>117980587</v>
       </c>
       <c r="B5" t="n">
-        <v>90464</v>
+        <v>90466</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117980680</v>
+        <v>117980710</v>
       </c>
       <c r="B6" t="n">
-        <v>90648</v>
+        <v>91774</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,25 +1103,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593615</v>
+        <v>593517</v>
       </c>
       <c r="R6" t="n">
-        <v>6982085</v>
+        <v>6982298</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117980689</v>
+        <v>117980680</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>90650</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,25 +1205,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593417</v>
+        <v>593615</v>
       </c>
       <c r="R7" t="n">
-        <v>6982462</v>
+        <v>6982085</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117980676</v>
+        <v>117980689</v>
       </c>
       <c r="B8" t="n">
-        <v>56270</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,25 +1307,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208260</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593679</v>
+        <v>593417</v>
       </c>
       <c r="R8" t="n">
-        <v>6982094</v>
+        <v>6982462</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1400,7 +1400,7 @@
         <v>117980637</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
